--- a/docs/StructureDefinition-ImplantableDevicePacemakerDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDevicePacemakerDevice.xlsx
@@ -60,13 +60,13 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-17T15:32:01+00:00</t>
+    <t>2023-10-31T15:37:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>JPSys</t>
+    <t>VA</t>
   </si>
   <si>
     <t>Contact</t>

--- a/docs/StructureDefinition-ImplantableDevicePacemakerDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDevicePacemakerDevice.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-31T15:37:13+00:00</t>
+    <t>2023-11-01T18:52:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for Use Case Implantable Device: Pacemaker, ResourceType Device</t>
+    <t>This StructureDefinition contains the maps for VistA GENERATOR IMPLANT (file 698) to FHIR Device</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/docs/StructureDefinition-ImplantableDevicePacemakerDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDevicePacemakerDevice.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2674" uniqueCount="388">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2673" uniqueCount="393">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-01T18:52:48+00:00</t>
+    <t>2023-11-08T21:21:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -114,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/us/core/StructureDefinition/us-core-implantable-device</t>
+    <t>http://va.gov/fhir/StructureDefinition/ImplantableDeviceDevice</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -627,6 +627,9 @@
   </si>
   <si>
     <t>The device identifier (DI), a mandatory, fixed portion of a UDI that identifies the labeler and the specific version or model of a device.</t>
+  </si>
+  <si>
+    <t>1353: target not supported</t>
   </si>
   <si>
     <t>Device.udiCarrier.issuer</t>
@@ -806,6 +809,9 @@
     <t>The lot or batch number within which a device was manufactured - which is a component of the production identifier (PI), a conditional, variable portion of a UDI.</t>
   </si>
   <si>
+    <t>1363: target not supported</t>
+  </si>
+  <si>
     <t>Device.manufacturer</t>
   </si>
   <si>
@@ -840,6 +846,9 @@
     <t>The date a specific device was manufactured - which is a component of the production identifier (PI), a conditional, variable portion of a UDI.  For FHIR, The datetime syntax must converted to YYYY-MM-DD[THH:MM:SS].  If hour is present, the minutes and seconds should both be set to “00”.</t>
   </si>
   <si>
+    <t>1371: target not supported</t>
+  </si>
+  <si>
     <t>Device.expirationDate</t>
   </si>
   <si>
@@ -855,6 +864,9 @@
     <t>the expiration date of a specific device -  which is a component of the production identifier (PI), a conditional, variable portion of a UDI.  For FHIR, The datetime syntax must converted to YYYY-MM-DD[THH:MM:SS].  If hour is present, the minutes and seconds should both be set to “00”.</t>
   </si>
   <si>
+    <t>1374: target not supported</t>
+  </si>
+  <si>
     <t>Device.lotNumber</t>
   </si>
   <si>
@@ -864,6 +876,9 @@
     <t>Lot number assigned by the manufacturer.</t>
   </si>
   <si>
+    <t>1377: target not supported</t>
+  </si>
+  <si>
     <t>Device.serialNumber</t>
   </si>
   <si>
@@ -889,6 +904,9 @@
   </si>
   <si>
     <t>This represents the manufacturer's name of the device as provided by the device, from a UDI label, or by a person describing the Device.  This typically would be used when a person provides the name(s) or when the device represents one of the names available from DeviceDefinition.</t>
+  </si>
+  <si>
+    <t>1386: target not supported</t>
   </si>
   <si>
     <t>Device.deviceName.id</t>
@@ -965,10 +983,7 @@
     <t>The kind or type of device.</t>
   </si>
   <si>
-    <t>Codes to identify medical devices</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/device-kind</t>
+    <t>http://va.gov/fhir/ValueSet/VFdeviceTypePacemaker</t>
   </si>
   <si>
     <t>1394: terminologyMaps using VF_deviceTypePacemaker on GENERATOR IMPLANT - PACEMAKER MODEL &gt; PACEMAKER EQUIPMENT - TYPE OF EQUIPMENT (#698-2 &gt; 698.4-1)</t>
@@ -1577,7 +1592,7 @@
     <col min="23" max="23" width="1.04296875" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="10.53125" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="98.375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="47.4921875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="48.9765625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="1.04296875" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="10.26171875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
@@ -4326,19 +4341,19 @@
         <v>194</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>37</v>
+        <v>195</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -4360,10 +4375,10 @@
         <v>59</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -4414,7 +4429,7 @@
         <v>37</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>38</v>
@@ -4429,13 +4444,13 @@
         <v>57</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AL25" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>37</v>
@@ -4443,10 +4458,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4472,14 +4487,14 @@
         <v>59</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>37</v>
@@ -4528,7 +4543,7 @@
         <v>37</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>38</v>
@@ -4543,7 +4558,7 @@
         <v>57</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AL26" t="s" s="2">
         <v>37</v>
@@ -4557,14 +4572,14 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
@@ -4583,16 +4598,16 @@
         <v>46</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -4642,7 +4657,7 @@
         <v>37</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>38</v>
@@ -4663,7 +4678,7 @@
         <v>37</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>37</v>
@@ -4671,14 +4686,14 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
@@ -4700,13 +4715,13 @@
         <v>111</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -4756,7 +4771,7 @@
         <v>37</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>38</v>
@@ -4777,7 +4792,7 @@
         <v>37</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>37</v>
@@ -4785,10 +4800,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4814,14 +4829,14 @@
         <v>65</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>37</v>
@@ -4849,10 +4864,10 @@
         <v>127</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>37</v>
@@ -4870,7 +4885,7 @@
         <v>37</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>38</v>
@@ -4885,7 +4900,7 @@
         <v>57</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AL29" t="s" s="2">
         <v>37</v>
@@ -4899,10 +4914,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4928,13 +4943,13 @@
         <v>65</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -4963,10 +4978,10 @@
         <v>127</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>37</v>
@@ -4984,7 +4999,7 @@
         <v>37</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>38</v>
@@ -4999,24 +5014,24 @@
         <v>57</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5042,10 +5057,10 @@
         <v>133</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -5075,10 +5090,10 @@
         <v>138</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>37</v>
@@ -5096,7 +5111,7 @@
         <v>37</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>38</v>
@@ -5114,7 +5129,7 @@
         <v>37</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>37</v>
@@ -5125,14 +5140,14 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -5154,13 +5169,13 @@
         <v>111</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5210,7 +5225,7 @@
         <v>37</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>38</v>
@@ -5225,24 +5240,24 @@
         <v>57</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>193</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>37</v>
+        <v>248</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5268,10 +5283,10 @@
         <v>111</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -5322,7 +5337,7 @@
         <v>37</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>38</v>
@@ -5337,7 +5352,7 @@
         <v>57</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>193</v>
@@ -5346,15 +5361,15 @@
         <v>88</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5377,13 +5392,13 @@
         <v>37</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5434,7 +5449,7 @@
         <v>37</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>38</v>
@@ -5449,24 +5464,24 @@
         <v>57</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>193</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>37</v>
+        <v>260</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5489,13 +5504,13 @@
         <v>37</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5546,7 +5561,7 @@
         <v>37</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>38</v>
@@ -5561,24 +5576,24 @@
         <v>57</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>193</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>37</v>
+        <v>266</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5604,10 +5619,10 @@
         <v>111</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5658,7 +5673,7 @@
         <v>37</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>38</v>
@@ -5673,24 +5688,24 @@
         <v>57</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>193</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>37</v>
+        <v>270</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5716,13 +5731,13 @@
         <v>111</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -5772,7 +5787,7 @@
         <v>37</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>38</v>
@@ -5787,7 +5802,7 @@
         <v>57</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>193</v>
@@ -5796,15 +5811,15 @@
         <v>37</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>271</v>
+        <v>276</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5830,10 +5845,10 @@
         <v>176</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -5884,7 +5899,7 @@
         <v>37</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>38</v>
@@ -5908,15 +5923,15 @@
         <v>37</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>37</v>
+        <v>280</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6025,10 +6040,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6139,10 +6154,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6255,14 +6270,14 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -6284,10 +6299,10 @@
         <v>111</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -6338,7 +6353,7 @@
         <v>37</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>45</v>
@@ -6367,10 +6382,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6396,10 +6411,10 @@
         <v>65</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -6429,10 +6444,10 @@
         <v>127</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>37</v>
@@ -6450,7 +6465,7 @@
         <v>37</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>45</v>
@@ -6465,7 +6480,7 @@
         <v>57</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>193</v>
@@ -6479,10 +6494,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6508,10 +6523,10 @@
         <v>111</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -6562,7 +6577,7 @@
         <v>37</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>38</v>
@@ -6577,7 +6592,7 @@
         <v>57</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>193</v>
@@ -6586,15 +6601,15 @@
         <v>37</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>292</v>
+        <v>298</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6620,13 +6635,13 @@
         <v>111</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -6676,7 +6691,7 @@
         <v>37</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>38</v>
@@ -6691,7 +6706,7 @@
         <v>57</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>193</v>
@@ -6705,10 +6720,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6734,10 +6749,10 @@
         <v>133</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -6764,13 +6779,11 @@
         <v>37</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="Y46" t="s" s="2">
-        <v>299</v>
-      </c>
+        <v>127</v>
+      </c>
+      <c r="Y46" s="2"/>
       <c r="Z46" t="s" s="2">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>37</v>
@@ -6788,7 +6801,7 @@
         <v>37</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>38</v>
@@ -6812,15 +6825,15 @@
         <v>37</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>301</v>
+        <v>306</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6846,10 +6859,10 @@
         <v>176</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -6900,7 +6913,7 @@
         <v>37</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>38</v>
@@ -6929,10 +6942,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7041,10 +7054,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7155,10 +7168,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7271,14 +7284,14 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -7300,10 +7313,10 @@
         <v>133</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7354,7 +7367,7 @@
         <v>37</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>45</v>
@@ -7383,10 +7396,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7412,10 +7425,10 @@
         <v>111</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -7466,7 +7479,7 @@
         <v>37</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>38</v>
@@ -7495,10 +7508,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7524,10 +7537,10 @@
         <v>176</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -7578,7 +7591,7 @@
         <v>37</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>38</v>
@@ -7607,10 +7620,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7719,10 +7732,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7833,10 +7846,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7949,14 +7962,14 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
@@ -7978,10 +7991,10 @@
         <v>133</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -8032,7 +8045,7 @@
         <v>37</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>38</v>
@@ -8061,10 +8074,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8090,10 +8103,10 @@
         <v>103</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -8144,7 +8157,7 @@
         <v>37</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>38</v>
@@ -8173,10 +8186,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8202,10 +8215,10 @@
         <v>111</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -8256,7 +8269,7 @@
         <v>37</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>45</v>
@@ -8285,10 +8298,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8314,10 +8327,10 @@
         <v>176</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -8368,7 +8381,7 @@
         <v>37</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>38</v>
@@ -8397,10 +8410,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8509,10 +8522,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8623,10 +8636,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8739,10 +8752,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -8768,10 +8781,10 @@
         <v>133</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -8822,7 +8835,7 @@
         <v>37</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>45</v>
@@ -8851,10 +8864,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -8877,13 +8890,13 @@
         <v>37</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -8934,7 +8947,7 @@
         <v>37</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>38</v>
@@ -8963,10 +8976,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -8992,10 +9005,10 @@
         <v>133</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -9046,7 +9059,7 @@
         <v>37</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>38</v>
@@ -9075,10 +9088,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9101,17 +9114,17 @@
         <v>37</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" t="s" s="2">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>37</v>
@@ -9160,7 +9173,7 @@
         <v>37</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>38</v>
@@ -9175,24 +9188,24 @@
         <v>57</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>352</v>
+        <v>357</v>
       </c>
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9218,10 +9231,10 @@
         <v>165</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -9272,7 +9285,7 @@
         <v>37</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>38</v>
@@ -9287,10 +9300,10 @@
         <v>57</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="AM68" t="s" s="2">
         <v>37</v>
@@ -9301,10 +9314,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9327,16 +9340,16 @@
         <v>37</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -9386,7 +9399,7 @@
         <v>37</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>38</v>
@@ -9401,10 +9414,10 @@
         <v>57</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="AM69" t="s" s="2">
         <v>37</v>
@@ -9415,10 +9428,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9441,17 +9454,17 @@
         <v>37</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" t="s" s="2">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>37</v>
@@ -9500,7 +9513,7 @@
         <v>37</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>38</v>
@@ -9515,10 +9528,10 @@
         <v>57</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="AM70" t="s" s="2">
         <v>37</v>
@@ -9529,10 +9542,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9558,13 +9571,13 @@
         <v>59</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -9614,7 +9627,7 @@
         <v>37</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>38</v>
@@ -9629,10 +9642,10 @@
         <v>57</v>
       </c>
       <c r="AK71" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="AL71" t="s" s="2">
         <v>375</v>
-      </c>
-      <c r="AL71" t="s" s="2">
-        <v>370</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>37</v>
@@ -9643,10 +9656,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -9669,13 +9682,13 @@
         <v>37</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -9726,7 +9739,7 @@
         <v>37</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>38</v>
@@ -9741,7 +9754,7 @@
         <v>57</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="AL72" t="s" s="2">
         <v>37</v>
@@ -9755,10 +9768,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -9784,10 +9797,10 @@
         <v>133</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -9838,7 +9851,7 @@
         <v>37</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>38</v>
@@ -9853,7 +9866,7 @@
         <v>57</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AL73" t="s" s="2">
         <v>37</v>
@@ -9867,10 +9880,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -9893,13 +9906,13 @@
         <v>37</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -9950,7 +9963,7 @@
         <v>37</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>38</v>

--- a/docs/StructureDefinition-ImplantableDevicePacemakerDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDevicePacemakerDevice.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-08T21:21:15+00:00</t>
+    <t>2023-11-08T21:56:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDevicePacemakerDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDevicePacemakerDevice.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-09T22:38:39+00:00</t>
+    <t>2023-11-14T14:54:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDevicePacemakerDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDevicePacemakerDevice.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-14T14:54:31+00:00</t>
+    <t>2023-11-14T17:25:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDevicePacemakerDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDevicePacemakerDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.3.0</t>
+    <t>0.4.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-14T17:25:19+00:00</t>
+    <t>2023-11-15T12:04:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDevicePacemakerDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDevicePacemakerDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.4.0</t>
+    <t>0.5.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-15T12:04:59+00:00</t>
+    <t>2023-11-15T19:14:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDevicePacemakerDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDevicePacemakerDevice.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-15T19:14:31+00:00</t>
+    <t>2023-11-15T20:37:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDevicePacemakerDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDevicePacemakerDevice.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-15T20:37:43+00:00</t>
+    <t>2023-11-29T20:32:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDevicePacemakerDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDevicePacemakerDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.0</t>
+    <t>0.6.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-29T20:32:59+00:00</t>
+    <t>2023-11-29T21:08:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDevicePacemakerDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDevicePacemakerDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.0</t>
+    <t>0.7.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-29T21:08:10+00:00</t>
+    <t>2023-12-12T19:04:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDevicePacemakerDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDevicePacemakerDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.7.0</t>
+    <t>0.9.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-12T19:04:11+00:00</t>
+    <t>2023-12-21T07:51:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDevicePacemakerDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDevicePacemakerDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.0</t>
+    <t>0.10.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-21T07:51:53+00:00</t>
+    <t>2023-12-21T16:22:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDevicePacemakerDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDevicePacemakerDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.10.0</t>
+    <t>0.11.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-21T16:22:28+00:00</t>
+    <t>2023-12-28T09:08:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDevicePacemakerDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDevicePacemakerDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.11.0</t>
+    <t>0.12.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-28T09:08:39+00:00</t>
+    <t>2023-12-29T17:54:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDevicePacemakerDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDevicePacemakerDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.12.0</t>
+    <t>0.13.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-29T17:54:36+00:00</t>
+    <t>2024-01-03T19:41:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA GENERATOR IMPLANT (file 698) to FHIR Device</t>
+    <t>This StructureDefinition contains the maps for VistA file GENERATOR IMPLANT (#698) to ImplantableDeviceDevice</t>
   </si>
   <si>
     <t>Purpose</t>
